--- a/pages/shp/uploads/27-08-2025 - 27-08-2025.xlsx
+++ b/pages/shp/uploads/27-08-2025 - 27-08-2025.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="336">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -339,34 +339,109 @@
     <t>KODE JENIS PENGANGKUTAN</t>
   </si>
   <si>
-    <t>00026174540620250827000359</t>
-  </si>
-  <si>
-    <t>261</t>
+    <t>00003074540620250827001360</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>040300</t>
   </si>
   <si>
     <t>050500</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>ITMIL</t>
+  </si>
+  <si>
+    <t>IDTPP</t>
+  </si>
+  <si>
+    <t>JPOSA</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-08-27</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
+    <t>DN</t>
+  </si>
+  <si>
     <t>BANDUNG</t>
   </si>
   <si>
-    <t>2025-08-27</t>
-  </si>
-  <si>
     <t>YUS YULIUS</t>
   </si>
   <si>
-    <t>EXIM MANAGER</t>
-  </si>
-  <si>
-    <t>IDR</t>
-  </si>
-  <si>
-    <t>018570</t>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>536778</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>00003074540620250827001362</t>
+  </si>
+  <si>
+    <t>050100</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>LK</t>
+  </si>
+  <si>
+    <t>IDCGK</t>
+  </si>
+  <si>
+    <t>LKCMB</t>
+  </si>
+  <si>
+    <t>LN</t>
+  </si>
+  <si>
+    <t>412536</t>
+  </si>
+  <si>
+    <t>00003074540620250827001361</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>CNSGN</t>
+  </si>
+  <si>
+    <t>412454</t>
   </si>
   <si>
     <t>KODE FASILITAS TARIF</t>
@@ -381,12 +456,6 @@
     <t>NPWP BILLING</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PPNLOKAL</t>
-  </si>
-  <si>
     <t>SERI</t>
   </si>
   <si>
@@ -429,100 +498,174 @@
     <t>KODE KATEGORI KONSOLIDATOR</t>
   </si>
   <si>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>PT NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL. RAYA RANCAEKEK MAJALAYA NO. 289 001/007 SOLOKANJERUK, SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
+    <t>JL. RAYA RANCAEKEK MAJALAYA NO. 289 RT. 001
+RW. 007 001/007 SOLOKANJERUK,
+SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0013166046051000000000</t>
+  </si>
+  <si>
+    <t>INDONESIAN AIR &amp; MARINE SUPPLY</t>
+  </si>
+  <si>
+    <t>JL.CILINCING RAYA33   CILINCING CILINCING KOTA ADM. JAKARTA UTARA DKI JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>DIESEL JAPAN CO LTD</t>
+  </si>
+  <si>
+    <t>NAMBA SKYO 25F, 
+5-1-60 NAMBA, CHUO-KU,			
+OSAKA 542-0076, 
+TEL: +81-6-6644-1955		
+</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>NIRWANA ALABARE GARMENT</t>
   </si>
   <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289289002007   SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
+    <t>JALAN RAYA RANCAEKAEK MAJALAYA NO.289 001/007 SOLOKANJERUK, SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>TEEJAY LANKA </t>
+  </si>
+  <si>
+    <t>BLOCK D8-D14, SEETHAWAKA, E.P.Z
+107000 AVISSAWELLA WESTERN PROVINCE
+SRILANKA
+</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289, SOLOKANJERUK, SOLOKANJERUK, KAB. BANDUNG, JAWA BARAT, 14111</t>
+  </si>
+  <si>
+    <t>0013107743062000000000</t>
+  </si>
+  <si>
+    <t>BIROTIKA SEMESTA</t>
+  </si>
+  <si>
+    <t>MULIA BUSINESS PARK BLD F, JL MT. HARYONO KAV 58-60, PANCORAN, PANCORAN, KOTA ADM. JAKARTA SELATAN, DKI JAKARTA, 53201</t>
+  </si>
+  <si>
+    <t>TONVEX GARMENT CO., LTD</t>
+  </si>
+  <si>
+    <t>YUNXING ROAD, SHAXI TOWN, ZHONGSHAN
+GUANGDONG 528400 ZHONGSHAN
+ATTN : WILLIAM LEUNG</t>
+  </si>
+  <si>
+    <t>0029142445012000000000</t>
+  </si>
+  <si>
+    <t>FEDEX EXPRESS INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>GEDUNG SOUTH QUARTER LT 12 TOWER C JL RADEN AJENG KARTINI KAV 8 RT.010 RW.004, CILANDAK BARAT, CILANDAK, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>920</t>
   </si>
   <si>
     <t>258/KM.4/WBC.09/2024</t>
   </si>
   <si>
-    <t>12-11-2024 00:00:00</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>0317950343528000000000</t>
-  </si>
-  <si>
-    <t>ECO LAUNDRY HIJAU INDONESIA</t>
-  </si>
-  <si>
-    <t>KARANGWARU,DESA/KELURAHAN KRIKILAN KEC.MASARAN KAB.SRAGEN PROVINSI JAWA TENAGH</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>636/TPB-SK.01/KBC.0903/2025</t>
-  </si>
-  <si>
-    <t>2025-08-15</t>
-  </si>
-  <si>
-    <t>315</t>
-  </si>
-  <si>
-    <t>136/NAG-ELH/KK/VIII/2025/002 </t>
-  </si>
-  <si>
-    <t>2025-08-12</t>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0359/E/NAG/0825 (005HIP2506SS26 )</t>
   </si>
   <si>
     <t>217</t>
   </si>
   <si>
+    <t>023340</t>
+  </si>
+  <si>
+    <t>2025-06-18</t>
+  </si>
+  <si>
+    <t>2024-12-12</t>
+  </si>
+  <si>
+    <t>0363/E/NAG/0825</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>082366</t>
-  </si>
-  <si>
-    <t>2025-07-30</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>01/NAG/VIII/2025</t>
+    <t>740</t>
+  </si>
+  <si>
+    <t>2451000425</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>OFC/OUT/0825/00210</t>
+  </si>
+  <si>
+    <t>0360/E/NAG/0825</t>
+  </si>
+  <si>
+    <t>883888091058</t>
   </si>
   <si>
     <t>KODE CARA ANGKUT</t>
@@ -546,6 +689,36 @@
     <t>CARA PENGANGKUTAN LAINNYA</t>
   </si>
   <si>
+    <t>SPIL KARTINI</t>
+  </si>
+  <si>
+    <t>V 007 N</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>K - MILE AIR</t>
+  </si>
+  <si>
+    <t>8K0801</t>
+  </si>
+  <si>
+    <t>TH</t>
+  </si>
+  <si>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>5194</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
     <t>KODE KEMASAN</t>
   </si>
   <si>
@@ -555,6 +728,9 @@
     <t>MEREK</t>
   </si>
   <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>PK</t>
   </si>
   <si>
@@ -723,19 +899,72 @@
     <t>61091010</t>
   </si>
   <si>
-    <t>HLT/0725/013</t>
-  </si>
-  <si>
-    <t>GARMENT/T-SHIRT UNTUK DI WASHING</t>
+    <t>DIE/0625/016</t>
+  </si>
+  <si>
+    <t>T-SHIRT SHORT SLEEVE
+MEN'SKNIT T-SHIRT (100% COTTON)
+ORDER NO  : CK_HK/2025/1123
+STYLE : A19963  
+COLOR : 9XX/ 100</t>
   </si>
   <si>
     <t>PCE</t>
   </si>
   <si>
+    <t>3204</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>HLT/0725/014</t>
+    <t>T-SHIRT SHORT SLEEVE
+MEN'SKNIT T-SHIRT (100% COTTON)
+ORDER NO  : CK_HK/2025/1122
+STYLE : A19963  
+COLOR : 100</t>
+  </si>
+  <si>
+    <t>T-SHIRT SHORT SLEEVE
+MEN'SKNIT T-SHIRT (100% COTTON)
+ORDER NO  : CK_HK/2025/1069
+STYLE : A19963  
+COLOR : 9XX</t>
+  </si>
+  <si>
+    <t>54082200</t>
+  </si>
+  <si>
+    <t>KN_4_KM_1</t>
+  </si>
+  <si>
+    <t>FABRIC SAMPLE
+(COTTON/MODAL/SP 57/38/5 SINGLE JERSEY)
+</t>
+  </si>
+  <si>
+    <t>YRD</t>
+  </si>
+  <si>
+    <t>62014010</t>
+  </si>
+  <si>
+    <t>SM/TVX/0825/001</t>
+  </si>
+  <si>
+    <t>SAMPLE BARANG JADI - BJT 903 JACKET HUMAN GREATNESS, COLOR : KHAKY</t>
+  </si>
+  <si>
+    <t>61033200</t>
+  </si>
+  <si>
+    <t>SAMPLE BARANG JADI - SP601 SHORT PANTS HUMAN GREATNESS, COLOR : MISTY</t>
+  </si>
+  <si>
+    <t>61102000</t>
+  </si>
+  <si>
+    <t>SAMPLE BARANG JADI - HUMAN GREATNESS, TSHIRT, &amp; POLO TOP, COLOR : BLACK, B25, PINK STRIPE, CURRY RED, DARK BROWN, RED TAPE</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -795,27 +1024,6 @@
     <t>VALUTA</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>52083900</t>
-  </si>
-  <si>
-    <t>2754</t>
-  </si>
-  <si>
-    <t>FABRIC KNIT 100% COTTON JERSEY 16S, ENZYME, COMPACT PFD</t>
-  </si>
-  <si>
-    <t>KGM</t>
-  </si>
-  <si>
-    <t>07-30-2025 00:00:00</t>
-  </si>
-  <si>
-    <t>00004074540620250730003646</t>
-  </si>
-  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -844,6 +1052,12 @@
   </si>
   <si>
     <t>NAMA</t>
+  </si>
+  <si>
+    <t>BANK CENTRAL ASIA</t>
+  </si>
+  <si>
+    <t>BANK BCA</t>
   </si>
   <si>
     <t>VERSI</t>
@@ -977,7 +1191,6 @@
     <col min="67" max="67" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="70" max="70" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="71" max="71" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="73" max="73" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="74" max="74" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="76" max="76" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="77" max="77" width="22.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1335,23 +1548,77 @@
       <c r="C2" t="s">
         <v>104</v>
       </c>
-      <c r="N2" t="s">
+      <c r="E2" t="s">
         <v>105</v>
       </c>
+      <c r="G2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>118</v>
+      </c>
       <c r="BK2" t="n">
-        <v>0.0</v>
+        <v>10.26</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0</v>
       </c>
+      <c r="BN2" t="n">
+        <v>0.0</v>
+      </c>
       <c r="BO2" t="n">
-        <v>0.0</v>
+        <v>10.26</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0</v>
+        <v>247.04</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0</v>
+        <v>4759.98</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1363,13 +1630,13 @@
         <v>0.0</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.31692176E7</v>
+        <v>0.0</v>
       </c>
       <c r="BV2" t="n">
         <v>0.0</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.0</v>
+        <v>16289.0</v>
       </c>
       <c r="BY2" t="n">
         <v>0.0</v>
@@ -1378,37 +1645,350 @@
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>135.6</v>
+        <v>148.73</v>
       </c>
       <c r="CC2" t="n">
-        <v>135.45</v>
+        <v>119.25</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0</v>
+        <v>0.114</v>
       </c>
       <c r="CE2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>123</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA2" t="s">
         <v>106</v>
       </c>
-      <c r="CF2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" t="s">
         <v>107</v>
       </c>
-      <c r="CG2" t="s">
-        <v>108</v>
-      </c>
-      <c r="CH2" t="s">
+      <c r="Q3" t="s">
+        <v>127</v>
+      </c>
+      <c r="W3" t="s">
         <v>109</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="AA3" t="s">
         <v>110</v>
       </c>
-      <c r="CP2" t="s">
-        <v>111</v>
-      </c>
-      <c r="CQ2" t="s">
+      <c r="AH3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ3" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I4" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" t="s">
         <v>107</v>
       </c>
-      <c r="CT2" t="n">
-        <v>0.0</v>
+      <c r="Q4" t="s">
+        <v>127</v>
+      </c>
+      <c r="W4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>134</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>116</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>126</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>136</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>116</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>124</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1439,10 +2019,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -1472,13 +2052,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1512,10 +2092,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1527,7 +2107,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -1548,13 +2128,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="56.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1564,7 +2142,7 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1587,64 +2165,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>188</v>
+        <v>243</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1659,218 +2237,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>253</v>
+        <v>321</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K2" t="s">
-        <v>158</v>
-      </c>
-      <c r="L2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M2" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="P2" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" t="s">
-        <v>160</v>
-      </c>
-      <c r="S2" t="s">
-        <v>259</v>
-      </c>
-      <c r="T2" t="s">
-        <v>260</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1093.35</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5267687.04</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G3" t="s">
-        <v>257</v>
-      </c>
-      <c r="H3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J3" t="s">
-        <v>158</v>
-      </c>
-      <c r="K3" t="s">
-        <v>158</v>
-      </c>
-      <c r="L3" t="s">
-        <v>258</v>
-      </c>
-      <c r="M3" t="n">
-        <v>73.15</v>
-      </c>
-      <c r="P3" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>104</v>
-      </c>
-      <c r="R3" t="s">
-        <v>160</v>
-      </c>
-      <c r="S3" t="s">
-        <v>259</v>
-      </c>
-      <c r="T3" t="s">
-        <v>260</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1093.35</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7901530.56</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -1891,7 +2303,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1922,164 +2334,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>579445.57</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>258</v>
-      </c>
-      <c r="N2" t="n">
-        <v>62.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>869168.36</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="M3" t="s">
-        <v>258</v>
-      </c>
-      <c r="N3" t="n">
-        <v>73.15</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -2113,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2470,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2158,30 +2482,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1448613.0</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2222,28 +2532,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -2264,7 +2574,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2272,13 +2583,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>248</v>
+        <v>316</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -2301,12 +2654,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>271</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -2331,12 +2684,12 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="28.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="95.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="31.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="170.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2348,46 +2701,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
@@ -2395,28 +2748,28 @@
         <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I2" t="s">
-        <v>137</v>
+        <v>157</v>
+      </c>
+      <c r="H2" t="s">
+        <v>158</v>
       </c>
       <c r="J2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
@@ -2424,37 +2777,22 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="F3" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" t="s">
-        <v>137</v>
-      </c>
-      <c r="J3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4">
@@ -2462,28 +2800,324 @@
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" t="s">
+        <v>168</v>
+      </c>
+      <c r="O4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G5" t="s">
+        <v>170</v>
+      </c>
+      <c r="M5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" t="s">
+        <v>170</v>
+      </c>
+      <c r="M7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" t="s">
+        <v>176</v>
+      </c>
+      <c r="M9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" t="s">
+        <v>176</v>
+      </c>
+      <c r="M11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="s">
+        <v>179</v>
+      </c>
+      <c r="F12" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" t="s">
+        <v>181</v>
+      </c>
+      <c r="O12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
         <v>133</v>
       </c>
-      <c r="E4" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G4" t="s">
-        <v>146</v>
-      </c>
-      <c r="I4" t="s">
-        <v>137</v>
-      </c>
-      <c r="J4" t="s">
-        <v>138</v>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" t="s">
+        <v>182</v>
+      </c>
+      <c r="G14" t="s">
+        <v>183</v>
+      </c>
+      <c r="M14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G15" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" t="s">
+        <v>168</v>
+      </c>
+      <c r="O15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" t="s">
+        <v>182</v>
+      </c>
+      <c r="G17" t="s">
+        <v>183</v>
+      </c>
+      <c r="M17" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2506,7 +3140,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="30.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="34.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2517,22 +3151,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>147</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2">
@@ -2543,13 +3177,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
@@ -2560,13 +3194,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -2577,13 +3211,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5">
@@ -2594,30 +3228,166 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="n">
         <v>5.0</v>
       </c>
-      <c r="C6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" t="s">
-        <v>107</v>
+      <c r="C10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2653,28 +3423,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>164</v>
+        <v>208</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2">
@@ -2685,7 +3455,56 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2716,16 +3535,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
@@ -2736,10 +3555,47 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2772,19 +3628,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2808,8 +3664,8 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="33.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="123.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2824,7 +3680,6 @@
     <col min="23" max="23" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="32" max="32" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2869,58 +3724,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>180</v>
+        <v>235</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>240</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>186</v>
+        <v>241</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>188</v>
+        <v>243</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>193</v>
+        <v>248</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -2932,19 +3787,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>195</v>
+        <v>250</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -2959,25 +3814,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>199</v>
+        <v>254</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>204</v>
+        <v>259</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -2986,82 +3841,82 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>206</v>
+        <v>261</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>209</v>
+        <v>264</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>210</v>
+        <v>265</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>219</v>
+        <v>274</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
@@ -3072,55 +3927,58 @@
         <v>102</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="F2" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="H2" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="J2" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="K2" t="n">
-        <v>252.0</v>
+        <v>4.0</v>
       </c>
       <c r="L2" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="M2" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T2" t="n">
-        <v>73.15</v>
+        <v>1.24</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.038</v>
       </c>
       <c r="Z2" t="n">
-        <v>7901530.56</v>
+        <v>0.0</v>
       </c>
       <c r="AA2" t="n">
-        <v>7901530.56</v>
+        <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.0</v>
+        <v>16289.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0</v>
+        <v>36.16</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -3134,6 +3992,9 @@
       <c r="AI2" t="n">
         <v>0.0</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>9.04</v>
+      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
@@ -3143,14 +4004,17 @@
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>139</v>
+      <c r="AS2" t="s">
+        <v>288</v>
       </c>
       <c r="AY2" t="s">
-        <v>233</v>
+        <v>289</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -3158,85 +4022,557 @@
         <v>102</v>
       </c>
       <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K3" t="n">
+        <v>244.0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>228</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2205.76</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>9.04</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" t="s">
+        <v>201</v>
+      </c>
+      <c r="G4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" t="n">
+        <v>274.0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2518.06</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" t="s">
+        <v>201</v>
+      </c>
+      <c r="G5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" t="s">
+        <v>201</v>
+      </c>
+      <c r="I5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" t="s">
+        <v>295</v>
+      </c>
+      <c r="K5" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="L5" t="s">
         <v>229</v>
       </c>
-      <c r="D3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J3" t="s">
-        <v>232</v>
-      </c>
-      <c r="K3" t="n">
-        <v>168.0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>174</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5267687.04</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>5267687.04</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="M5" t="n">
         <v>1.0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>233</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.0</v>
+      <c r="T5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J6" t="s">
+        <v>287</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>229</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F7" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J7" t="s">
+        <v>287</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>229</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G8" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" t="s">
+        <v>201</v>
+      </c>
+      <c r="I8" t="s">
+        <v>201</v>
+      </c>
+      <c r="J8" t="s">
+        <v>287</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>229</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16289.0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>288</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>289</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3282,58 +4618,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -3354,7 +4690,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3365,35 +4701,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
